--- a/dcf/BEPC.xlsx
+++ b/dcf/BEPC.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.03549100571010785</v>
+        <v>0.03523161159204925</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.04049100571010785</v>
+        <v>0.04023161159204925</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.04549100571010786</v>
+        <v>0.04523161159204925</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.05049100571010785</v>
+        <v>0.05023161159204925</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.05549100571010785</v>
+        <v>0.05523161159204925</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.06049100571010785</v>
+        <v>0.06023161159204925</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.06549100571010785</v>
+        <v>0.06523161159204925</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>11.5209820868755</v>
+        <v>11.77671977673315</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>6.726230596683894</v>
+        <v>6.968795001653705</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>2.177846990284648</v>
+        <v>2.407976172311477</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>-2.137938350472117</v>
+        <v>-1.919550938053463</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>-6.234064816958477</v>
+        <v>-6.026767439013167</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>-10.12269523905392</v>
+        <v>-9.925875187974926</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>-13.81526585083832</v>
+        <v>-13.628346940956</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>22.96635210629921</v>
+        <v>23.25080039000933</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>17.63334436583305</v>
+        <v>17.90313749572622</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>12.57441832021177</v>
+        <v>12.83037740544512</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>7.774254975232262</v>
+        <v>8.017151497885511</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>3.218458964983169</v>
+        <v>3.449017995540975</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>-1.106501149027188</v>
+        <v>-0.8875979583870192</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>-5.213348463200179</v>
+        <v>-5.005460091209603</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>34.41172212572288</v>
+        <v>34.72488100328551</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>28.5404581349822</v>
+        <v>28.83747998979877</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>22.97098965013885</v>
+        <v>23.25277863857876</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>17.68644830093664</v>
+        <v>17.95385393382444</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>12.67098274692477</v>
+        <v>12.92480343009508</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>7.909692940999515</v>
+        <v>8.150679271200868</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>3.388568924437935</v>
+        <v>3.617426758536784</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>45.85709214514659</v>
+        <v>46.19896161656165</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>39.44757190413135</v>
+        <v>39.77182248387128</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>33.36756098006593</v>
+        <v>33.67517987171236</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>27.59864162664102</v>
+        <v>27.89055636976342</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>22.12350652886642</v>
+        <v>22.40058886464918</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>16.92588703102622</v>
+        <v>17.18895650078876</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>11.99048631207609</v>
+        <v>12.24031360828317</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>57.3024621645703</v>
+        <v>57.67304222983784</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>50.35468567328055</v>
+        <v>50.7061649779438</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>43.76413230999305</v>
+        <v>44.097581104846</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>37.5108349523454</v>
+        <v>37.82725880570235</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>31.57603031080807</v>
+        <v>31.87637429920332</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>25.94208112105292</v>
+        <v>26.22723373037664</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>20.5924036997142</v>
+        <v>20.86320045802956</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>68.74783218399401</v>
+        <v>69.14712284311402</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>61.2617994424297</v>
+        <v>61.64050747201631</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>54.16070363992013</v>
+        <v>54.51998233797964</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>47.42302827804978</v>
+        <v>47.76396124164132</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>41.02855409274967</v>
+        <v>41.35215973375746</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>34.95827521107967</v>
+        <v>35.26551095996453</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>29.19432108735236</v>
+        <v>29.48608730777594</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>80.19320220341767</v>
+        <v>80.62120345639016</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>72.16891321157885</v>
+        <v>72.57484996608883</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>64.55727496984721</v>
+        <v>64.94238357111328</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>57.33522160375411</v>
+        <v>57.70066367758025</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>50.48107787469132</v>
+        <v>50.82794516831157</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>43.97446930110637</v>
+        <v>44.30378818955241</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>37.79623847499047</v>
+        <v>38.10897415752233</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>36.4900016784668</v>
+        <v>35.69499969482422</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.05049100571010785</v>
+        <v>0.05023161159204925</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.5178052577538126</v>
+        <v>0.519343834594398</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>36.4900016784668</v>
+        <v>35.69499969482422</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>27.59864162664102</v>
+        <v>27.89055636976342</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>80.08857977198696</v>
+        <v>80.50485575761927</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>-13.17391196007868</v>
+        <v>-12.97799098347773</v>
       </c>
     </row>
     <row r="59">
